--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_17-07-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_17-07-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00D7092-6660-43DD-836C-0B83403B58E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03AFDAF-7DC0-4A5B-90D3-0D4D9182D407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29415" yWindow="2175" windowWidth="21600" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32985" yWindow="2475" windowWidth="21600" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -775,9 +775,6 @@
     <t>£59.43</t>
   </si>
   <si>
-    <t>£15.39</t>
-  </si>
-  <si>
     <t>£18.10</t>
   </si>
   <si>
@@ -830,6 +827,9 @@
   </si>
   <si>
     <t>£716.05</t>
+  </si>
+  <si>
+    <t>£276.59</t>
   </si>
 </sst>
 </file>
@@ -1295,7 +1295,7 @@
         <v>40</v>
       </c>
       <c r="O2" t="s">
-        <v>251</v>
+        <v>28</v>
       </c>
       <c r="P2" t="s">
         <v>29</v>
@@ -1351,7 +1351,7 @@
         <v>52</v>
       </c>
       <c r="O3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P3" t="s">
         <v>29</v>
@@ -1407,7 +1407,7 @@
         <v>64</v>
       </c>
       <c r="O4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P4" t="s">
         <v>29</v>
@@ -1463,7 +1463,7 @@
         <v>76</v>
       </c>
       <c r="O5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P5" t="s">
         <v>29</v>
@@ -1519,7 +1519,7 @@
         <v>88</v>
       </c>
       <c r="O6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P6" t="s">
         <v>29</v>
@@ -1575,7 +1575,7 @@
         <v>29</v>
       </c>
       <c r="O7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P7" t="s">
         <v>29</v>
@@ -1687,7 +1687,7 @@
         <v>119</v>
       </c>
       <c r="O9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P9" t="s">
         <v>29</v>
@@ -1743,7 +1743,7 @@
         <v>29</v>
       </c>
       <c r="O10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P10" t="s">
         <v>29</v>
@@ -1799,7 +1799,7 @@
         <v>139</v>
       </c>
       <c r="O11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P11" t="s">
         <v>29</v>
@@ -1911,7 +1911,7 @@
         <v>171</v>
       </c>
       <c r="O13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P13" t="s">
         <v>29</v>
@@ -1967,7 +1967,7 @@
         <v>160</v>
       </c>
       <c r="O14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P14" t="s">
         <v>29</v>
@@ -2023,7 +2023,7 @@
         <v>182</v>
       </c>
       <c r="O15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P15" t="s">
         <v>29</v>
@@ -2076,7 +2076,7 @@
         <v>181</v>
       </c>
       <c r="N16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O16" t="s">
         <v>183</v>
@@ -2099,7 +2099,7 @@
         <v>187</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>269</v>
       </c>
       <c r="D17" t="s">
         <v>29</v>
@@ -2188,7 +2188,7 @@
         <v>26</v>
       </c>
       <c r="N18" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O18" t="s">
         <v>193</v>
@@ -2244,7 +2244,7 @@
         <v>26</v>
       </c>
       <c r="N19" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O19" t="s">
         <v>200</v>
@@ -2459,7 +2459,7 @@
         <v>26</v>
       </c>
       <c r="K23" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L23" t="s">
         <v>26</v>
@@ -2468,7 +2468,7 @@
         <v>219</v>
       </c>
       <c r="N23" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O23" t="s">
         <v>220</v>
@@ -2515,7 +2515,7 @@
         <v>26</v>
       </c>
       <c r="K24" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="L24" t="s">
         <v>26</v>
@@ -2524,7 +2524,7 @@
         <v>29</v>
       </c>
       <c r="N24" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O24" t="s">
         <v>226</v>
@@ -2580,7 +2580,7 @@
         <v>29</v>
       </c>
       <c r="N25" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O25" t="s">
         <v>234</v>
